--- a/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝--地图.xlsx
+++ b/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝--地图.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\myMod\InesMod\InesMod\src\main\resources\InesModResources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D651B44-9909-4BCC-A128-0BE750B6DAC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F9C4BB8-875B-4E12-9905-13B16C04EB5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11752" yWindow="0" windowWidth="11370" windowHeight="13763" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="12">
   <si>
     <t>T</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -172,9 +172,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -455,15 +455,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A6:AI18"/>
+  <dimension ref="A5:AI18"/>
   <sheetFormatPr defaultColWidth="6.1328125" defaultRowHeight="22.05" customHeight="1" x14ac:dyDescent="0.4"/>
   <sheetData>
+    <row r="5" spans="1:35" ht="22.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="AC5" s="1"/>
+      <c r="AD5" s="1"/>
+      <c r="AE5" s="1"/>
+      <c r="AF5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG5" s="1"/>
+      <c r="AH5" s="1"/>
+      <c r="AI5" s="1"/>
+    </row>
     <row r="6" spans="1:35" ht="22.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
-      <c r="N6" s="3" t="s">
-        <v>7</v>
+      <c r="N6" s="7" t="s">
+        <v>6</v>
       </c>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
@@ -471,8 +491,8 @@
       <c r="AC6" s="1"/>
       <c r="AD6" s="1"/>
       <c r="AE6" s="1"/>
-      <c r="AF6" s="3" t="s">
-        <v>7</v>
+      <c r="AF6" s="7" t="s">
+        <v>6</v>
       </c>
       <c r="AG6" s="1"/>
       <c r="AH6" s="1"/>
@@ -494,10 +514,10 @@
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="M7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
@@ -517,8 +537,8 @@
       <c r="AC7" s="1"/>
       <c r="AD7" s="1"/>
       <c r="AE7" s="1"/>
-      <c r="AF7" s="7" t="s">
-        <v>6</v>
+      <c r="AF7" s="2" t="s">
+        <v>2</v>
       </c>
       <c r="AG7" s="1"/>
       <c r="AH7" s="1"/>
@@ -539,10 +559,10 @@
         <v>7</v>
       </c>
       <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="2" t="s">
-        <v>2</v>
-      </c>
+      <c r="L8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="M8" s="1"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
@@ -563,10 +583,10 @@
       <c r="AC8" s="1"/>
       <c r="AD8" s="1"/>
       <c r="AE8" s="1"/>
-      <c r="AF8" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AG8" s="1"/>
+      <c r="AF8" s="1"/>
+      <c r="AG8" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="AH8" s="1"/>
       <c r="AI8" s="1"/>
     </row>
@@ -577,7 +597,9 @@
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
+      <c r="E9" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
@@ -585,11 +607,10 @@
         <v>6</v>
       </c>
       <c r="K9" s="1"/>
-      <c r="L9" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
@@ -598,7 +619,9 @@
       </c>
       <c r="T9" s="1"/>
       <c r="U9" s="1"/>
-      <c r="W9" s="1"/>
+      <c r="W9" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
@@ -609,8 +632,8 @@
       <c r="AD9" s="1"/>
       <c r="AE9" s="1"/>
       <c r="AF9" s="1"/>
-      <c r="AG9" s="2" t="s">
-        <v>4</v>
+      <c r="AG9" s="5" t="s">
+        <v>1</v>
       </c>
       <c r="AH9" s="1"/>
       <c r="AI9" s="1"/>
@@ -621,9 +644,8 @@
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="3" t="s">
-        <v>7</v>
+      <c r="E10" s="7" t="s">
+        <v>6</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -633,8 +655,8 @@
       </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
-      <c r="M10" s="6" t="s">
-        <v>5</v>
+      <c r="N10" s="4" t="s">
+        <v>0</v>
       </c>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
@@ -644,8 +666,9 @@
       </c>
       <c r="T10" s="1"/>
       <c r="U10" s="1"/>
-      <c r="W10" s="3" t="s">
-        <v>7</v>
+      <c r="V10" s="1"/>
+      <c r="W10" s="7" t="s">
+        <v>6</v>
       </c>
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
@@ -656,10 +679,10 @@
       <c r="AC10" s="1"/>
       <c r="AD10" s="1"/>
       <c r="AE10" s="1"/>
-      <c r="AF10" s="1"/>
-      <c r="AG10" s="6" t="s">
-        <v>5</v>
-      </c>
+      <c r="AF10" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="1"/>
       <c r="AH10" s="1"/>
       <c r="AI10" s="1"/>
     </row>
@@ -669,10 +692,13 @@
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="E11" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" s="1"/>
+      <c r="D11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="2" t="s">
+        <v>2</v>
+      </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="J11">
@@ -680,10 +706,11 @@
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
-      <c r="N11" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="O11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="2" t="s">
+        <v>2</v>
+      </c>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
       <c r="S11">
@@ -691,11 +718,12 @@
       </c>
       <c r="T11" s="1"/>
       <c r="U11" s="1"/>
-      <c r="V11" s="1"/>
-      <c r="W11" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="X11" s="1"/>
+      <c r="V11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="W11" s="2" t="s">
+        <v>2</v>
+      </c>
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
       <c r="AB11">
@@ -703,11 +731,10 @@
       </c>
       <c r="AC11" s="1"/>
       <c r="AD11" s="1"/>
-      <c r="AE11" s="1"/>
-      <c r="AF11" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="AG11" s="1"/>
+      <c r="AE11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AF11" s="1"/>
       <c r="AH11" s="1"/>
       <c r="AI11" s="1"/>
     </row>
@@ -716,15 +743,17 @@
         <v>3</v>
       </c>
       <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E12" s="1"/>
-      <c r="F12" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G12" s="1"/>
+      <c r="C12" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="H12" s="1"/>
       <c r="J12">
         <v>3</v>
@@ -732,21 +761,23 @@
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="P12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="Q12" s="1"/>
       <c r="S12">
         <v>3</v>
       </c>
       <c r="T12" s="1"/>
       <c r="U12" s="1"/>
-      <c r="V12" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="W12" s="2" t="s">
+      <c r="V12" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="W12" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="X12" s="2" t="s">
         <v>2</v>
       </c>
       <c r="Y12" s="1"/>
@@ -757,7 +788,7 @@
       <c r="AC12" s="1"/>
       <c r="AD12" s="1"/>
       <c r="AE12" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF12" s="1"/>
       <c r="AH12" s="1"/>
@@ -768,17 +799,15 @@
         <v>2</v>
       </c>
       <c r="B13" s="1"/>
-      <c r="C13" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="F13" s="1"/>
-      <c r="G13" s="2" t="s">
-        <v>4</v>
-      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="J13">
         <v>2</v>
@@ -786,24 +815,23 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="2" t="s">
-        <v>4</v>
-      </c>
+      <c r="N13" s="1"/>
+      <c r="O13" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
       <c r="S13">
         <v>2</v>
       </c>
       <c r="T13" s="1"/>
       <c r="U13" s="1"/>
-      <c r="V13" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="W13" s="4" t="s">
-        <v>0</v>
+      <c r="V13" s="1"/>
+      <c r="W13" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
@@ -812,10 +840,11 @@
       </c>
       <c r="AC13" s="1"/>
       <c r="AD13" s="1"/>
-      <c r="AE13" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF13" s="1"/>
+      <c r="AE13" s="1"/>
+      <c r="AF13" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG13" s="1"/>
       <c r="AH13" s="1"/>
       <c r="AI13" s="1"/>
     </row>
@@ -825,13 +854,11 @@
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
-      <c r="D14" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="1"/>
-      <c r="F14" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="J14">
@@ -840,10 +867,10 @@
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="N14" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
       <c r="S14">
@@ -852,12 +879,10 @@
       <c r="T14" s="1"/>
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
-      <c r="W14" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="X14" s="2" t="s">
-        <v>4</v>
-      </c>
+      <c r="W14" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
       <c r="AB14">
@@ -866,8 +891,8 @@
       <c r="AC14" s="1"/>
       <c r="AD14" s="1"/>
       <c r="AE14" s="1"/>
-      <c r="AF14" s="2" t="s">
-        <v>3</v>
+      <c r="AF14" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="AG14" s="1"/>
       <c r="AH14" s="1"/>

--- a/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝--地图.xlsx
+++ b/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝--地图.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\myMod\InesMod\InesMod\src\main\resources\InesModResources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F9C4BB8-875B-4E12-9905-13B16C04EB5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6403498-7411-433C-9614-2797C26BAA41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="12">
   <si>
     <t>T</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -455,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A5:AI18"/>
+  <dimension ref="A5:AI17"/>
   <sheetFormatPr defaultColWidth="6.1328125" defaultRowHeight="22.05" customHeight="1" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="5" spans="1:35" ht="22.05" customHeight="1" x14ac:dyDescent="0.4">
@@ -479,6 +479,19 @@
       <c r="AI5" s="1"/>
     </row>
     <row r="6" spans="1:35" ht="22.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="J6">
+        <v>8</v>
+      </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -488,6 +501,19 @@
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
+      <c r="S6">
+        <v>8</v>
+      </c>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+      <c r="X6" s="1"/>
+      <c r="Y6" s="1"/>
+      <c r="Z6" s="1"/>
+      <c r="AB6">
+        <v>8</v>
+      </c>
       <c r="AC6" s="1"/>
       <c r="AD6" s="1"/>
       <c r="AE6" s="1"/>
@@ -500,7 +526,7 @@
     </row>
     <row r="7" spans="1:35" ht="22.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -510,7 +536,7 @@
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="J7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
@@ -522,7 +548,7 @@
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
       <c r="S7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
@@ -532,7 +558,7 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
       <c r="AB7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC7" s="1"/>
       <c r="AD7" s="1"/>
@@ -546,7 +572,7 @@
     </row>
     <row r="8" spans="1:35" ht="22.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -556,7 +582,7 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="J8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="2" t="s">
@@ -568,7 +594,7 @@
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
       <c r="S8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T8" s="1"/>
       <c r="U8" s="1"/>
@@ -578,7 +604,7 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
       <c r="AB8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC8" s="1"/>
       <c r="AD8" s="1"/>
@@ -592,7 +618,7 @@
     </row>
     <row r="9" spans="1:35" ht="22.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -604,18 +630,18 @@
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="J9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
-      <c r="M9" s="6" t="s">
-        <v>5</v>
+      <c r="M9" s="5" t="s">
+        <v>1</v>
       </c>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
       <c r="S9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T9" s="1"/>
       <c r="U9" s="1"/>
@@ -626,7 +652,7 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
       <c r="AB9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC9" s="1"/>
       <c r="AD9" s="1"/>
@@ -640,7 +666,7 @@
     </row>
     <row r="10" spans="1:35" ht="22.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -651,7 +677,7 @@
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="J10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
@@ -662,7 +688,7 @@
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
       <c r="S10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T10" s="1"/>
       <c r="U10" s="1"/>
@@ -674,7 +700,7 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
       <c r="AB10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC10" s="1"/>
       <c r="AD10" s="1"/>
@@ -688,7 +714,7 @@
     </row>
     <row r="11" spans="1:35" ht="22.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -702,7 +728,7 @@
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="J11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
@@ -714,7 +740,7 @@
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
       <c r="S11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T11" s="1"/>
       <c r="U11" s="1"/>
@@ -727,7 +753,7 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
       <c r="AB11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC11" s="1"/>
       <c r="AD11" s="1"/>
@@ -740,7 +766,7 @@
     </row>
     <row r="12" spans="1:35" ht="22.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="2" t="s">
@@ -752,22 +778,22 @@
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H12" s="1"/>
       <c r="J12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q12" s="1"/>
       <c r="S12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T12" s="1"/>
       <c r="U12" s="1"/>
@@ -783,12 +809,12 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
       <c r="AB12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC12" s="1"/>
       <c r="AD12" s="1"/>
       <c r="AE12" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF12" s="1"/>
       <c r="AH12" s="1"/>
@@ -796,7 +822,7 @@
     </row>
     <row r="13" spans="1:35" ht="22.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -804,45 +830,45 @@
         <v>1</v>
       </c>
       <c r="E13" s="1"/>
-      <c r="F13" s="2" t="s">
-        <v>3</v>
+      <c r="F13" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="J13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
-      <c r="O13" s="2" t="s">
-        <v>3</v>
+      <c r="O13" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
       <c r="S13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T13" s="1"/>
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
-      <c r="W13" s="2" t="s">
-        <v>3</v>
+      <c r="W13" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
       <c r="AB13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC13" s="1"/>
       <c r="AD13" s="1"/>
       <c r="AE13" s="1"/>
-      <c r="AF13" s="2" t="s">
-        <v>3</v>
+      <c r="AF13" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="AG13" s="1"/>
       <c r="AH13" s="1"/>
@@ -850,201 +876,151 @@
     </row>
     <row r="14" spans="1:35" ht="22.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
-      <c r="E14" s="6" t="s">
-        <v>5</v>
+      <c r="E14" s="5" t="s">
+        <v>1</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="J14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
-      <c r="N14" s="6" t="s">
-        <v>5</v>
+      <c r="N14" s="5" t="s">
+        <v>1</v>
       </c>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
       <c r="S14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T14" s="1"/>
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
-      <c r="W14" s="6" t="s">
-        <v>5</v>
+      <c r="W14" s="5" t="s">
+        <v>1</v>
       </c>
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
       <c r="AB14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC14" s="1"/>
       <c r="AD14" s="1"/>
       <c r="AE14" s="1"/>
-      <c r="AF14" s="6" t="s">
-        <v>5</v>
+      <c r="AF14" s="5" t="s">
+        <v>1</v>
       </c>
       <c r="AG14" s="1"/>
       <c r="AH14" s="1"/>
       <c r="AI14" s="1"/>
     </row>
     <row r="15" spans="1:35" ht="22.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15">
-        <v>0</v>
-      </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
-      <c r="Q15" s="1"/>
-      <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="T15" s="1"/>
-      <c r="U15" s="1"/>
-      <c r="V15" s="1"/>
-      <c r="W15" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="X15" s="1"/>
-      <c r="Y15" s="1"/>
-      <c r="Z15" s="1"/>
-      <c r="AB15">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="1"/>
-      <c r="AD15" s="1"/>
-      <c r="AE15" s="1"/>
-      <c r="AF15" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG15" s="1"/>
-      <c r="AH15" s="1"/>
-      <c r="AI15" s="1"/>
-    </row>
-    <row r="16" spans="1:35" ht="22.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16">
-        <v>0</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>2</v>
-      </c>
-      <c r="E16">
-        <v>3</v>
-      </c>
-      <c r="F16">
-        <v>4</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-      <c r="H16">
-        <v>6</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>1</v>
-      </c>
-      <c r="M16">
-        <v>2</v>
-      </c>
-      <c r="N16">
-        <v>3</v>
-      </c>
-      <c r="O16">
-        <v>4</v>
-      </c>
-      <c r="P16">
-        <v>5</v>
-      </c>
-      <c r="Q16">
-        <v>6</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>1</v>
-      </c>
-      <c r="V16">
-        <v>2</v>
-      </c>
-      <c r="W16">
-        <v>3</v>
-      </c>
-      <c r="X16">
-        <v>4</v>
-      </c>
-      <c r="Y16">
-        <v>5</v>
-      </c>
-      <c r="Z16">
-        <v>6</v>
-      </c>
-      <c r="AC16">
-        <v>0</v>
-      </c>
-      <c r="AD16">
-        <v>1</v>
-      </c>
-      <c r="AE16">
-        <v>2</v>
-      </c>
-      <c r="AF16">
-        <v>3</v>
-      </c>
-      <c r="AG16">
-        <v>4</v>
-      </c>
-      <c r="AH16">
-        <v>5</v>
-      </c>
-      <c r="AI16">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="5:32" ht="22.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="E18" t="s">
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+      <c r="E15">
+        <v>3</v>
+      </c>
+      <c r="F15">
+        <v>4</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+      <c r="H15">
+        <v>6</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>2</v>
+      </c>
+      <c r="N15">
+        <v>3</v>
+      </c>
+      <c r="O15">
+        <v>4</v>
+      </c>
+      <c r="P15">
+        <v>5</v>
+      </c>
+      <c r="Q15">
+        <v>6</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>1</v>
+      </c>
+      <c r="V15">
+        <v>2</v>
+      </c>
+      <c r="W15">
+        <v>3</v>
+      </c>
+      <c r="X15">
+        <v>4</v>
+      </c>
+      <c r="Y15">
+        <v>5</v>
+      </c>
+      <c r="Z15">
+        <v>6</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>1</v>
+      </c>
+      <c r="AE15">
+        <v>2</v>
+      </c>
+      <c r="AF15">
+        <v>3</v>
+      </c>
+      <c r="AG15">
+        <v>4</v>
+      </c>
+      <c r="AH15">
+        <v>5</v>
+      </c>
+      <c r="AI15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="5:32" ht="22.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E17" t="s">
         <v>8</v>
       </c>
-      <c r="N18" t="s">
+      <c r="N17" t="s">
         <v>9</v>
       </c>
-      <c r="W18" t="s">
+      <c r="W17" t="s">
         <v>10</v>
       </c>
-      <c r="AF18" t="s">
+      <c r="AF17" t="s">
         <v>11</v>
       </c>
     </row>
